--- a/nr-add-profile-list/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/nr-add-profile-list/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3015" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3051" uniqueCount="494">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T10:18:04+00:00</t>
+    <t>2024-03-21T10:58:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -630,6 +630,23 @@
   </si>
   <si>
     <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.extension:specialty</t>
+  </si>
+  <si>
+    <t>specialty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner-specialty}
+</t>
+  </si>
+  <si>
+    <t>FR Core Practitioner Specialty Extension</t>
+  </si>
+  <si>
+    <t>This extension adds the element "specialty" to the FHIR Practitioner resource.
+http://esante.gouv.fr/sites/NOS/TABS/TRE_R38-SpecialiteOrdinale.tabs</t>
   </si>
   <si>
     <t>Practitioner.modifierExtension</t>
@@ -1852,7 +1869,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN82"/>
+  <dimension ref="A1:AN83"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.38671875" customWidth="true" bestFit="true"/>
@@ -1865,7 +1882,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="75.65234375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="79.90625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -3957,43 +3974,41 @@
         <v>198</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="C19" s="2"/>
+        <v>195</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="D19" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>111</v>
+        <v>200</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>201</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>77</v>
       </c>
@@ -4029,19 +4044,19 @@
         <v>77</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4059,7 +4074,7 @@
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -4077,7 +4092,7 @@
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4090,23 +4105,25 @@
         <v>77</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O20" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>77</v>
@@ -4143,10 +4160,10 @@
         <v>77</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>208</v>
+        <v>115</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>209</v>
+        <v>116</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>77</v>
@@ -4155,7 +4172,7 @@
         <v>117</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4167,27 +4184,27 @@
         <v>100</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>210</v>
+        <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>211</v>
+        <v>102</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>212</v>
+        <v>77</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>213</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4198,7 +4215,7 @@
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>77</v>
@@ -4207,19 +4224,21 @@
         <v>77</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>104</v>
+        <v>209</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>105</v>
+        <v>210</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>106</v>
+        <v>211</v>
       </c>
       <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
+      <c r="O21" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>77</v>
       </c>
@@ -4255,62 +4274,62 @@
         <v>77</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>77</v>
+        <v>213</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>77</v>
+        <v>214</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>107</v>
+        <v>208</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>77</v>
+        <v>215</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>108</v>
+        <v>216</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>77</v>
+        <v>217</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>77</v>
+        <v>218</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>77</v>
@@ -4322,17 +4341,15 @@
         <v>77</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -4369,37 +4386,37 @@
         <v>77</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
@@ -4410,46 +4427,44 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>172</v>
+        <v>111</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>217</v>
+        <v>112</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>218</v>
+        <v>113</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>220</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>77</v>
       </c>
@@ -4473,49 +4488,49 @@
         <v>77</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>221</v>
+        <v>77</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>222</v>
+        <v>77</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>223</v>
+        <v>77</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>224</v>
+        <v>118</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>102</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -4526,10 +4541,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4546,25 +4561,25 @@
         <v>77</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>227</v>
+        <v>172</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4589,11 +4604,13 @@
         <v>77</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="Y24" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="Z24" t="s" s="2">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>77</v>
@@ -4611,7 +4628,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4626,10 +4643,10 @@
         <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>234</v>
+        <v>102</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
@@ -4640,10 +4657,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4663,19 +4680,23 @@
         <v>77</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>104</v>
+        <v>232</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>105</v>
+        <v>233</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
       </c>
@@ -4699,13 +4720,11 @@
         <v>77</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>77</v>
+        <v>237</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>77</v>
@@ -4723,7 +4742,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>107</v>
+        <v>238</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4732,16 +4751,16 @@
         <v>88</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>77</v>
+        <v>239</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>108</v>
+        <v>230</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -4752,21 +4771,21 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>77</v>
@@ -4778,17 +4797,15 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4825,37 +4842,37 @@
         <v>77</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4866,14 +4883,14 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4889,23 +4906,21 @@
         <v>77</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>238</v>
+        <v>112</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>239</v>
+        <v>113</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>241</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>77</v>
       </c>
@@ -4941,19 +4956,19 @@
         <v>77</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>242</v>
+        <v>118</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4965,13 +4980,13 @@
         <v>100</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>243</v>
+        <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>244</v>
+        <v>102</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -4982,10 +4997,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4996,7 +5011,7 @@
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>77</v>
@@ -5005,19 +5020,23 @@
         <v>77</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>104</v>
+        <v>148</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>105</v>
+        <v>243</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>77</v>
       </c>
@@ -5065,25 +5084,25 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>107</v>
+        <v>247</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>77</v>
+        <v>248</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>108</v>
+        <v>249</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -5094,21 +5113,21 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>77</v>
@@ -5120,17 +5139,15 @@
         <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -5167,37 +5184,37 @@
         <v>77</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
@@ -5208,21 +5225,21 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>77</v>
@@ -5231,23 +5248,21 @@
         <v>77</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>248</v>
+        <v>112</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>249</v>
+        <v>113</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>77</v>
       </c>
@@ -5259,7 +5274,7 @@
         <v>77</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>252</v>
+        <v>77</v>
       </c>
       <c r="U30" t="s" s="2">
         <v>77</v>
@@ -5283,37 +5298,37 @@
         <v>77</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>253</v>
+        <v>118</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>254</v>
+        <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>255</v>
+        <v>102</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
@@ -5324,10 +5339,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5350,18 +5365,20 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>255</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>256</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
       </c>
@@ -5373,7 +5390,7 @@
         <v>77</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>77</v>
+        <v>257</v>
       </c>
       <c r="U31" t="s" s="2">
         <v>77</v>
@@ -5409,7 +5426,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5424,10 +5441,10 @@
         <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
@@ -5438,10 +5455,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5464,20 +5481,18 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>172</v>
+        <v>104</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N32" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="M32" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>267</v>
-      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>77</v>
       </c>
@@ -5525,7 +5540,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5540,10 +5555,10 @@
         <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
@@ -5554,10 +5569,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5580,19 +5595,19 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>104</v>
+        <v>172</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="O33" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5641,7 +5656,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5656,10 +5671,10 @@
         <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
@@ -5670,10 +5685,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5696,19 +5711,19 @@
         <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="O34" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="L34" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5757,7 +5772,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5772,10 +5787,10 @@
         <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
@@ -5786,10 +5801,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5812,19 +5827,19 @@
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>104</v>
+        <v>284</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="O35" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5873,7 +5888,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5888,10 +5903,10 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
@@ -5902,10 +5917,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5913,7 +5928,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>88</v>
@@ -5928,19 +5943,19 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="O36" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5953,7 +5968,7 @@
         <v>77</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>300</v>
+        <v>77</v>
       </c>
       <c r="U36" t="s" s="2">
         <v>77</v>
@@ -5989,7 +6004,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6004,13 +6019,13 @@
         <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>304</v>
+        <v>77</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>77</v>
@@ -6018,10 +6033,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6044,18 +6059,20 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
       </c>
@@ -6067,7 +6084,7 @@
         <v>77</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>77</v>
@@ -6103,7 +6120,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6118,13 +6135,13 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>77</v>
@@ -6132,10 +6149,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6143,7 +6160,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>88</v>
@@ -6158,16 +6175,16 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>315</v>
+        <v>104</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6181,7 +6198,7 @@
         <v>77</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>77</v>
+        <v>314</v>
       </c>
       <c r="U38" t="s" s="2">
         <v>77</v>
@@ -6217,7 +6234,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6229,16 +6246,16 @@
         <v>100</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>320</v>
+        <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>77</v>
@@ -6246,10 +6263,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6272,16 +6289,16 @@
         <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6331,7 +6348,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6343,16 +6360,16 @@
         <v>100</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>77</v>
@@ -6360,14 +6377,12 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="C40" t="s" s="2">
-        <v>335</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>77</v>
       </c>
@@ -6388,18 +6403,18 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>204</v>
+        <v>330</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>77</v>
       </c>
@@ -6447,41 +6462,43 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>203</v>
+        <v>334</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>101</v>
+        <v>335</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>210</v>
+        <v>336</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>211</v>
+        <v>337</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>212</v>
+        <v>338</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>213</v>
+        <v>77</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="C41" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="D41" t="s" s="2">
         <v>77</v>
       </c>
@@ -6499,19 +6516,21 @@
         <v>77</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>104</v>
+        <v>209</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>105</v>
+        <v>341</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>106</v>
+        <v>211</v>
       </c>
       <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+      <c r="O41" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>77</v>
       </c>
@@ -6559,50 +6578,50 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>107</v>
+        <v>208</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>77</v>
+        <v>215</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>108</v>
+        <v>216</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>77</v>
+        <v>217</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>77</v>
+        <v>218</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>77</v>
@@ -6614,17 +6633,15 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>77</v>
@@ -6661,37 +6678,37 @@
         <v>77</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -6702,46 +6719,44 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>172</v>
+        <v>111</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>217</v>
+        <v>112</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>218</v>
+        <v>113</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>220</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>77</v>
       </c>
@@ -6765,49 +6780,49 @@
         <v>77</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>221</v>
+        <v>77</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>222</v>
+        <v>77</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>223</v>
+        <v>77</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>224</v>
+        <v>118</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>102</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>77</v>
@@ -6818,10 +6833,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6838,25 +6853,25 @@
         <v>77</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J44" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>227</v>
+        <v>172</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>341</v>
+        <v>222</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6866,7 +6881,7 @@
         <v>77</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>342</v>
+        <v>77</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>77</v>
@@ -6881,13 +6896,13 @@
         <v>77</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>152</v>
+        <v>226</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>343</v>
+        <v>227</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>344</v>
+        <v>228</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>77</v>
@@ -6905,7 +6920,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6920,10 +6935,10 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>234</v>
+        <v>102</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
@@ -6937,7 +6952,7 @@
         <v>345</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>295</v>
+        <v>231</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6960,19 +6975,19 @@
         <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>132</v>
+        <v>232</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>296</v>
+        <v>346</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>346</v>
+        <v>234</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>298</v>
+        <v>235</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>299</v>
+        <v>236</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6985,7 +7000,7 @@
         <v>347</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>300</v>
+        <v>77</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>77</v>
@@ -6997,13 +7012,13 @@
         <v>77</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>77</v>
+        <v>348</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>77</v>
+        <v>349</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>77</v>
@@ -7021,7 +7036,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>301</v>
+        <v>238</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7036,13 +7051,13 @@
         <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>302</v>
+        <v>239</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>303</v>
+        <v>230</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>304</v>
+        <v>77</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>77</v>
@@ -7050,10 +7065,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7076,18 +7091,20 @@
         <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>349</v>
+        <v>301</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>307</v>
+        <v>351</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
       </c>
@@ -7096,10 +7113,10 @@
         <v>77</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>77</v>
+        <v>352</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>77</v>
@@ -7135,7 +7152,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7150,13 +7167,13 @@
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>77</v>
@@ -7164,10 +7181,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7190,16 +7207,16 @@
         <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>315</v>
+        <v>104</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>316</v>
+        <v>354</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7213,7 +7230,7 @@
         <v>77</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>77</v>
+        <v>314</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>77</v>
@@ -7249,7 +7266,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7261,16 +7278,16 @@
         <v>100</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>320</v>
+        <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>77</v>
@@ -7278,10 +7295,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7304,16 +7321,16 @@
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7363,7 +7380,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7375,16 +7392,16 @@
         <v>100</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>77</v>
@@ -7392,14 +7409,12 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="C49" t="s" s="2">
-        <v>353</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>77</v>
       </c>
@@ -7408,7 +7423,7 @@
         <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>77</v>
@@ -7420,18 +7435,18 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>204</v>
+        <v>330</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>354</v>
+        <v>331</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>77</v>
       </c>
@@ -7479,41 +7494,43 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>203</v>
+        <v>334</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>101</v>
+        <v>335</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>210</v>
+        <v>336</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>211</v>
+        <v>337</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>212</v>
+        <v>338</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>213</v>
+        <v>77</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="C50" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="C50" t="s" s="2">
+        <v>358</v>
+      </c>
       <c r="D50" t="s" s="2">
         <v>77</v>
       </c>
@@ -7522,7 +7539,7 @@
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>77</v>
@@ -7531,19 +7548,21 @@
         <v>77</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>104</v>
+        <v>209</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>105</v>
+        <v>359</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>106</v>
+        <v>211</v>
       </c>
       <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+      <c r="O50" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
       </c>
@@ -7591,50 +7610,50 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>107</v>
+        <v>208</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>77</v>
+        <v>215</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>108</v>
+        <v>216</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>77</v>
+        <v>217</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>77</v>
+        <v>218</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>77</v>
@@ -7646,17 +7665,15 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>77</v>
@@ -7693,37 +7710,37 @@
         <v>77</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -7734,46 +7751,44 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>172</v>
+        <v>111</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>217</v>
+        <v>112</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>218</v>
+        <v>113</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>220</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>77</v>
       </c>
@@ -7797,49 +7812,49 @@
         <v>77</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>221</v>
+        <v>77</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>222</v>
+        <v>77</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>223</v>
+        <v>77</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>224</v>
+        <v>118</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL52" t="s" s="2">
         <v>102</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>77</v>
@@ -7850,10 +7865,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7870,25 +7885,25 @@
         <v>77</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J53" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>227</v>
+        <v>172</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>77</v>
@@ -7898,7 +7913,7 @@
         <v>77</v>
       </c>
       <c r="S53" t="s" s="2">
-        <v>359</v>
+        <v>77</v>
       </c>
       <c r="T53" t="s" s="2">
         <v>77</v>
@@ -7913,13 +7928,13 @@
         <v>77</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>152</v>
+        <v>226</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>343</v>
+        <v>227</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>344</v>
+        <v>228</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>77</v>
@@ -7937,7 +7952,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7952,10 +7967,10 @@
         <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>234</v>
+        <v>102</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>77</v>
@@ -7966,10 +7981,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>295</v>
+        <v>231</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7992,19 +8007,19 @@
         <v>89</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>132</v>
+        <v>232</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>296</v>
+        <v>233</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>346</v>
+        <v>234</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>298</v>
+        <v>235</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>299</v>
+        <v>236</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -8014,10 +8029,10 @@
         <v>77</v>
       </c>
       <c r="S54" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>300</v>
+        <v>77</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>77</v>
@@ -8029,13 +8044,13 @@
         <v>77</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>77</v>
+        <v>348</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>77</v>
+        <v>349</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>77</v>
@@ -8053,7 +8068,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>301</v>
+        <v>238</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8068,13 +8083,13 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>302</v>
+        <v>239</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>303</v>
+        <v>230</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>304</v>
+        <v>77</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>77</v>
@@ -8082,10 +8097,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8108,18 +8123,20 @@
         <v>89</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>307</v>
+        <v>351</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>77</v>
       </c>
@@ -8128,10 +8145,10 @@
         <v>77</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>77</v>
+        <v>366</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>77</v>
@@ -8167,7 +8184,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8182,13 +8199,13 @@
         <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>77</v>
@@ -8196,10 +8213,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8222,16 +8239,16 @@
         <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>315</v>
+        <v>104</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8245,7 +8262,7 @@
         <v>77</v>
       </c>
       <c r="T56" t="s" s="2">
-        <v>77</v>
+        <v>314</v>
       </c>
       <c r="U56" t="s" s="2">
         <v>77</v>
@@ -8281,7 +8298,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8293,16 +8310,16 @@
         <v>100</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>320</v>
+        <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>77</v>
@@ -8310,10 +8327,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8336,16 +8353,16 @@
         <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8395,7 +8412,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8407,16 +8424,16 @@
         <v>100</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>77</v>
@@ -8424,14 +8441,12 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="C58" t="s" s="2">
-        <v>366</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
         <v>77</v>
       </c>
@@ -8440,7 +8455,7 @@
         <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>77</v>
@@ -8452,18 +8467,18 @@
         <v>89</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>204</v>
+        <v>330</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>367</v>
+        <v>331</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>77</v>
       </c>
@@ -8511,41 +8526,43 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>203</v>
+        <v>334</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>101</v>
+        <v>335</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>210</v>
+        <v>336</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>211</v>
+        <v>337</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>212</v>
+        <v>338</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>213</v>
+        <v>77</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="C59" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="C59" t="s" s="2">
+        <v>371</v>
+      </c>
       <c r="D59" t="s" s="2">
         <v>77</v>
       </c>
@@ -8554,7 +8571,7 @@
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>77</v>
@@ -8563,19 +8580,21 @@
         <v>77</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>104</v>
+        <v>209</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>105</v>
+        <v>372</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>106</v>
+        <v>211</v>
       </c>
       <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+      <c r="O59" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
       </c>
@@ -8623,50 +8642,50 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>107</v>
+        <v>208</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>77</v>
+        <v>215</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>108</v>
+        <v>216</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>77</v>
+        <v>217</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>77</v>
+        <v>218</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>77</v>
@@ -8678,17 +8697,15 @@
         <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>77</v>
@@ -8725,37 +8742,37 @@
         <v>77</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
@@ -8766,46 +8783,44 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>172</v>
+        <v>111</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>217</v>
+        <v>112</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>218</v>
+        <v>113</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>220</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>77</v>
       </c>
@@ -8829,49 +8844,49 @@
         <v>77</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>221</v>
+        <v>77</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>222</v>
+        <v>77</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>223</v>
+        <v>77</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>224</v>
+        <v>118</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL61" t="s" s="2">
         <v>102</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
@@ -8882,10 +8897,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8902,25 +8917,25 @@
         <v>77</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J62" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>227</v>
+        <v>172</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>77</v>
@@ -8930,7 +8945,7 @@
         <v>77</v>
       </c>
       <c r="S62" t="s" s="2">
-        <v>372</v>
+        <v>77</v>
       </c>
       <c r="T62" t="s" s="2">
         <v>77</v>
@@ -8945,13 +8960,13 @@
         <v>77</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>152</v>
+        <v>226</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>343</v>
+        <v>227</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>344</v>
+        <v>228</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>77</v>
@@ -8969,7 +8984,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8984,10 +8999,10 @@
         <v>101</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>234</v>
+        <v>102</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
@@ -8998,10 +9013,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>295</v>
+        <v>231</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9024,19 +9039,19 @@
         <v>89</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>132</v>
+        <v>232</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>296</v>
+        <v>233</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>346</v>
+        <v>234</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>298</v>
+        <v>235</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>299</v>
+        <v>236</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -9046,10 +9061,10 @@
         <v>77</v>
       </c>
       <c r="S63" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="T63" t="s" s="2">
-        <v>300</v>
+        <v>77</v>
       </c>
       <c r="U63" t="s" s="2">
         <v>77</v>
@@ -9061,13 +9076,13 @@
         <v>77</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>77</v>
+        <v>348</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>77</v>
+        <v>349</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>77</v>
@@ -9085,7 +9100,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>301</v>
+        <v>238</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9100,13 +9115,13 @@
         <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>302</v>
+        <v>239</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>303</v>
+        <v>230</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>304</v>
+        <v>77</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>77</v>
@@ -9114,10 +9129,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9140,18 +9155,20 @@
         <v>89</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>307</v>
+        <v>351</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="O64" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>77</v>
       </c>
@@ -9160,10 +9177,10 @@
         <v>77</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>77</v>
+        <v>379</v>
       </c>
       <c r="T64" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="U64" t="s" s="2">
         <v>77</v>
@@ -9199,7 +9216,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9214,13 +9231,13 @@
         <v>101</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>77</v>
@@ -9228,10 +9245,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9254,16 +9271,16 @@
         <v>89</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>315</v>
+        <v>104</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9277,7 +9294,7 @@
         <v>77</v>
       </c>
       <c r="T65" t="s" s="2">
-        <v>77</v>
+        <v>314</v>
       </c>
       <c r="U65" t="s" s="2">
         <v>77</v>
@@ -9313,7 +9330,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9325,16 +9342,16 @@
         <v>100</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>320</v>
+        <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>77</v>
@@ -9342,10 +9359,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9368,16 +9385,16 @@
         <v>89</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9427,7 +9444,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9439,16 +9456,16 @@
         <v>100</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>77</v>
@@ -9456,10 +9473,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>378</v>
+        <v>329</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9482,26 +9499,22 @@
         <v>89</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>279</v>
+        <v>330</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>379</v>
+        <v>331</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>380</v>
+        <v>332</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>382</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q67" t="s" s="2">
-        <v>383</v>
-      </c>
+      <c r="Q67" s="2"/>
       <c r="R67" t="s" s="2">
         <v>77</v>
       </c>
@@ -9545,7 +9558,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>378</v>
+        <v>334</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9557,27 +9570,27 @@
         <v>100</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>101</v>
+        <v>335</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>77</v>
+        <v>336</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>384</v>
+        <v>337</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>77</v>
+        <v>338</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>385</v>
+        <v>77</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9588,7 +9601,7 @@
         <v>78</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>77</v>
@@ -9597,27 +9610,29 @@
         <v>77</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="O68" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="P68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q68" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="M68" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="P68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q68" s="2"/>
       <c r="R68" t="s" s="2">
         <v>77</v>
       </c>
@@ -9661,13 +9676,13 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>100</v>
@@ -9676,24 +9691,24 @@
         <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>392</v>
+        <v>77</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>394</v>
+        <v>77</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>77</v>
+        <v>390</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9716,19 +9731,19 @@
         <v>77</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="O69" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>77</v>
@@ -9777,7 +9792,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9789,16 +9804,16 @@
         <v>100</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>401</v>
+        <v>101</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>77</v>
@@ -9806,10 +9821,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9832,19 +9847,19 @@
         <v>77</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>77</v>
@@ -9893,7 +9908,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -9905,16 +9920,16 @@
         <v>100</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>101</v>
+        <v>406</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>77</v>
@@ -9922,10 +9937,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9936,7 +9951,7 @@
         <v>78</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>77</v>
@@ -9945,22 +9960,22 @@
         <v>77</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>172</v>
+        <v>411</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="O71" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>77</v>
@@ -9985,13 +10000,13 @@
         <v>77</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>221</v>
+        <v>77</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>418</v>
+        <v>77</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>419</v>
+        <v>77</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>77</v>
@@ -10009,13 +10024,13 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>100</v>
@@ -10024,13 +10039,13 @@
         <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>77</v>
@@ -10038,10 +10053,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10064,17 +10079,19 @@
         <v>89</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>424</v>
+        <v>172</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>421</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>271</v>
+      </c>
       <c r="O72" t="s" s="2">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>77</v>
@@ -10099,13 +10116,13 @@
         <v>77</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>77</v>
+        <v>226</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>77</v>
+        <v>423</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>77</v>
+        <v>424</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>77</v>
@@ -10123,7 +10140,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10138,13 +10155,13 @@
         <v>101</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>77</v>
@@ -10152,10 +10169,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10166,7 +10183,7 @@
         <v>78</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>77</v>
@@ -10175,22 +10192,20 @@
         <v>77</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>77</v>
@@ -10239,28 +10254,28 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>437</v>
+        <v>101</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>77</v>
@@ -10268,10 +10283,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10294,16 +10309,20 @@
         <v>77</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
+        <v>439</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>77</v>
       </c>
@@ -10351,7 +10370,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10363,16 +10382,16 @@
         <v>100</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>101</v>
+        <v>442</v>
       </c>
       <c r="AK74" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AM74" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>77</v>
@@ -10380,10 +10399,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10394,7 +10413,7 @@
         <v>78</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>77</v>
@@ -10406,13 +10425,13 @@
         <v>77</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>104</v>
+        <v>447</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>105</v>
+        <v>448</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>106</v>
+        <v>449</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10463,28 +10482,28 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>107</v>
+        <v>446</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>77</v>
+        <v>450</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>108</v>
+        <v>451</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>77</v>
+        <v>452</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>77</v>
@@ -10492,21 +10511,21 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>77</v>
@@ -10518,17 +10537,15 @@
         <v>77</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>77</v>
@@ -10565,37 +10582,37 @@
         <v>77</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>77</v>
@@ -10606,14 +10623,14 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>451</v>
+        <v>110</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -10626,26 +10643,24 @@
         <v>77</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K77" t="s" s="2">
         <v>111</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>452</v>
+        <v>112</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>453</v>
+        <v>113</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="O77" t="s" s="2">
-        <v>201</v>
-      </c>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>77</v>
       </c>
@@ -10681,19 +10696,19 @@
         <v>77</v>
       </c>
       <c r="AB77" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC77" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>454</v>
+        <v>118</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -10729,7 +10744,7 @@
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>77</v>
+        <v>456</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -10742,23 +10757,25 @@
         <v>77</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>204</v>
+        <v>111</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N78" s="2"/>
+        <v>458</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O78" t="s" s="2">
-        <v>458</v>
+        <v>206</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>77</v>
@@ -10807,7 +10824,7 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -10819,16 +10836,16 @@
         <v>100</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>459</v>
+        <v>77</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>460</v>
+        <v>102</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>461</v>
+        <v>77</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>77</v>
@@ -10836,10 +10853,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10847,10 +10864,10 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>77</v>
@@ -10862,18 +10879,18 @@
         <v>77</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="M79" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>77</v>
       </c>
@@ -10897,11 +10914,13 @@
         <v>77</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="Y79" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z79" t="s" s="2">
-        <v>466</v>
+        <v>77</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>77</v>
@@ -10919,13 +10938,13 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>100</v>
@@ -10934,13 +10953,13 @@
         <v>101</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>446</v>
+        <v>465</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>77</v>
@@ -10948,10 +10967,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10959,7 +10978,7 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G80" t="s" s="2">
         <v>88</v>
@@ -10974,20 +10993,18 @@
         <v>77</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>315</v>
+        <v>232</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="N80" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="M80" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>472</v>
-      </c>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>77</v>
       </c>
@@ -11011,13 +11028,11 @@
         <v>77</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
-        <v>77</v>
+        <v>471</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>77</v>
@@ -11035,10 +11050,10 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>88</v>
@@ -11047,16 +11062,16 @@
         <v>100</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>320</v>
+        <v>101</v>
       </c>
       <c r="AK80" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AM80" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>77</v>
@@ -11064,10 +11079,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11090,18 +11105,20 @@
         <v>77</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="O81" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="M81" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>77</v>
       </c>
@@ -11149,7 +11166,7 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11161,16 +11178,16 @@
         <v>100</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>77</v>
+        <v>478</v>
       </c>
       <c r="AL81" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AM81" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>77</v>
@@ -11192,7 +11209,7 @@
         <v>78</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>77</v>
@@ -11204,7 +11221,7 @@
         <v>77</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>227</v>
+        <v>330</v>
       </c>
       <c r="L82" t="s" s="2">
         <v>482</v>
@@ -11215,9 +11232,7 @@
       <c r="N82" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="O82" t="s" s="2">
-        <v>485</v>
-      </c>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>77</v>
       </c>
@@ -11241,13 +11256,13 @@
         <v>77</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>177</v>
+        <v>77</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>77</v>
@@ -11271,24 +11286,140 @@
         <v>78</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ82" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="P83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AK82" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="AN82" t="s" s="2">
+      <c r="AK83" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AN83" t="s" s="2">
         <v>77</v>
       </c>
     </row>

--- a/nr-add-profile-list/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/nr-add-profile-list/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T10:58:03+00:00</t>
+    <t>2024-03-21T10:59:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-profile-list/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/nr-add-profile-list/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T10:59:21+00:00</t>
+    <t>2024-03-21T12:49:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-profile-list/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/nr-add-profile-list/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T12:49:37+00:00</t>
+    <t>2024-03-21T12:55:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-profile-list/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/nr-add-profile-list/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T12:55:50+00:00</t>
+    <t>2024-03-22T10:25:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-profile-list/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/nr-add-profile-list/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T10:25:22+00:00</t>
+    <t>2024-03-22T13:38:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-profile-list/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/nr-add-profile-list/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T13:38:23+00:00</t>
+    <t>2024-03-25T10:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
